--- a/서버정보/20260716_리소스배포_랜딩.xlsx
+++ b/서버정보/20260716_리소스배포_랜딩.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EF1A29-BB0D-499D-800A-188882CADB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7450998-4E38-45E5-99C8-27FEFF3ACDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VM" sheetId="1" r:id="rId1"/>
@@ -1658,7 +1658,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="340">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2903,10 +2903,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>COM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-l-if-hipsproxy01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2923,15 +2919,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>COM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>l-if-hipsproxy01-disk01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>l-if-hipsproxy01-disk02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-l-if-cpspsol01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.136</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D32s_v5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-l-comm-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>l-if-cpspsol01-disk02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>l-if-cpspsol01-disk01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4929,8 +4949,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF10" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
-  <autoFilter ref="B1:AF10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF11" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="B1:AF11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
@@ -5274,7 +5294,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -6118,26 +6138,28 @@
       <c r="AF9" s="88"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A10" s="84"/>
       <c r="B10" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C10" s="106" t="s">
-        <v>327</v>
-      </c>
-      <c r="D10" s="106" t="s">
+      <c r="C10" s="88" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($F10, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D10" s="88" t="s">
         <v>145</v>
       </c>
       <c r="E10" s="88" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="88" t="s">
+        <v>327</v>
+      </c>
+      <c r="G10" s="88" t="s">
         <v>328</v>
       </c>
-      <c r="G10" s="88" t="s">
+      <c r="H10" s="88" t="s">
         <v>329</v>
-      </c>
-      <c r="H10" s="88" t="s">
-        <v>330</v>
       </c>
       <c r="I10" s="88">
         <v>2</v>
@@ -6155,9 +6177,9 @@
         <v>292</v>
       </c>
       <c r="N10" s="97" t="s">
-        <v>331</v>
-      </c>
-      <c r="O10" s="107" t="str">
+        <v>330</v>
+      </c>
+      <c r="O10" s="98" t="str">
         <f>SUBSTITUTE(F10,"hazr-","")&amp;"-osdisk"</f>
         <v>l-if-hipsproxy01-osdisk</v>
       </c>
@@ -6167,10 +6189,10 @@
       <c r="Q10" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R10" s="106"/>
+      <c r="R10" s="88"/>
       <c r="S10" s="88"/>
-      <c r="T10" s="106"/>
-      <c r="U10" s="106" t="str">
+      <c r="T10" s="88"/>
+      <c r="U10" s="88" t="str">
         <f>SUBSTITUTE(F10,"hazr-","")&amp;"-nic"</f>
         <v>l-if-hipsproxy01-nic</v>
       </c>
@@ -6203,6 +6225,94 @@
       </c>
       <c r="AE10" s="88"/>
       <c r="AF10" s="88"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11" s="88" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" s="106" t="str" cm="1">
+        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D11" s="106" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="88" t="s">
+        <v>333</v>
+      </c>
+      <c r="G11" s="88" t="s">
+        <v>334</v>
+      </c>
+      <c r="H11" s="88" t="s">
+        <v>336</v>
+      </c>
+      <c r="I11" s="88">
+        <v>32</v>
+      </c>
+      <c r="J11" s="88">
+        <v>128</v>
+      </c>
+      <c r="K11" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="L11" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="N11" s="97" t="s">
+        <v>335</v>
+      </c>
+      <c r="O11" s="107" t="str">
+        <f>SUBSTITUTE(F11,"hazr-","")&amp;"-osdisk"</f>
+        <v>l-if-cpspsol01-osdisk</v>
+      </c>
+      <c r="P11" s="99">
+        <v>64</v>
+      </c>
+      <c r="Q11" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="R11" s="106"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="106"/>
+      <c r="U11" s="88" t="str">
+        <f>SUBSTITUTE(F11,"hazr-","")&amp;"-nic"</f>
+        <v>l-if-cpspsol01-nic</v>
+      </c>
+      <c r="V11" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y11" s="88" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z11" s="88" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA11" s="88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC11" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD11" s="99">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="88"/>
+      <c r="AF11" s="88"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6219,7 +6329,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" style="70" customWidth="1"/>
@@ -6719,11 +6829,13 @@
       <c r="R9" s="69"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="92"/>
       <c r="B10" s="103" t="s">
         <v>321</v>
       </c>
-      <c r="C10" s="103" t="s">
-        <v>332</v>
+      <c r="C10" s="104" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($F10, "-"), 3))</f>
+        <v>IF</v>
       </c>
       <c r="D10" s="104" t="s">
         <v>145</v>
@@ -6732,10 +6844,10 @@
         <v>24</v>
       </c>
       <c r="F10" s="103" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G10" s="103" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H10" s="103" t="s">
         <v>121</v>
@@ -6744,7 +6856,7 @@
         <v>128</v>
       </c>
       <c r="J10" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K10" s="103" t="s">
         <v>121</v>
@@ -6768,6 +6880,58 @@
         <v>1</v>
       </c>
       <c r="R10" s="103"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" s="69" t="str" cm="1">
+        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="G11" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="69">
+        <v>2048</v>
+      </c>
+      <c r="J11" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="K11" s="75" t="s">
+        <v>121</v>
+      </c>
+      <c r="L11" s="69">
+        <v>128</v>
+      </c>
+      <c r="M11" s="69">
+        <v>1</v>
+      </c>
+      <c r="N11" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="O11" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="P11" s="69" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q11" s="69" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="69"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:R9" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}"/>
@@ -7970,7 +8134,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5" customWidth="1"/>
@@ -8304,6 +8468,7 @@
       <c r="M8" s="68"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="84"/>
       <c r="B9" s="75" t="s">
         <v>321</v>
       </c>
@@ -8315,39 +8480,41 @@
         <v>145</v>
       </c>
       <c r="E9" s="75" t="str">
-        <f t="shared" ref="E9:E10" si="5">SUBSTITUTE(I9,"hazr-","")&amp;"-nsg"</f>
+        <f t="shared" ref="E9:E11" si="5">SUBSTITUTE(I9,"hazr-","")&amp;"-nsg"</f>
         <v>l-com-scmsol01-nsg</v>
       </c>
-      <c r="F9" s="69" t="s">
+      <c r="F9" s="75" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="75" t="s">
         <v>290</v>
       </c>
-      <c r="I9" s="101" t="s">
+      <c r="I9" s="75" t="s">
         <v>322</v>
       </c>
-      <c r="J9" s="69" t="s">
+      <c r="J9" s="75" t="s">
         <v>145</v>
       </c>
-      <c r="K9" s="69" t="str">
+      <c r="K9" s="75" t="str">
         <f t="shared" ref="K9:K10" si="6">SUBSTITUTE(I9,"hazr-","")&amp;"-nic"</f>
         <v>l-com-scmsol01-nic</v>
       </c>
-      <c r="L9" s="76" t="s">
+      <c r="L9" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="M9" s="69"/>
+      <c r="M9" s="75"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="84"/>
       <c r="B10" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="C10" s="73" t="s">
-        <v>332</v>
+      <c r="C10" s="73" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($E10, "-"), 2))</f>
+        <v>IF</v>
       </c>
       <c r="D10" s="73" t="s">
         <v>145</v>
@@ -8356,29 +8523,68 @@
         <f t="shared" si="5"/>
         <v>l-if-hipsproxy01-nsg</v>
       </c>
-      <c r="F10" s="68" t="s">
+      <c r="F10" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="73" t="s">
         <v>138</v>
       </c>
-      <c r="H10" s="68" t="s">
+      <c r="H10" s="73" t="s">
         <v>290</v>
       </c>
-      <c r="I10" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="J10" s="68" t="s">
+      <c r="I10" s="73" t="s">
+        <v>327</v>
+      </c>
+      <c r="J10" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="K10" s="68" t="str">
+      <c r="K10" s="73" t="str">
         <f t="shared" si="6"/>
         <v>l-if-hipsproxy01-nic</v>
       </c>
-      <c r="L10" s="74" t="s">
+      <c r="L10" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="M10" s="68"/>
+      <c r="M10" s="73"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="75" t="s">
+        <v>321</v>
+      </c>
+      <c r="C11" s="75" t="str" cm="1">
+        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($E11, "-"), 2))</f>
+        <v>IF</v>
+      </c>
+      <c r="D11" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="75" t="str">
+        <f t="shared" si="5"/>
+        <v>l-if-cpspsol01-nsg</v>
+      </c>
+      <c r="F11" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="H11" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="I11" s="75" t="s">
+        <v>333</v>
+      </c>
+      <c r="J11" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="K11" s="75" t="str">
+        <f t="shared" ref="K11" si="7">SUBSTITUTE(I11,"hazr-","")&amp;"-nic"</f>
+        <v>l-if-cpspsol01-nic</v>
+      </c>
+      <c r="L11" s="75" t="s">
+        <v>141</v>
+      </c>
+      <c r="M11" s="75"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:M9" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}"/>

--- a/서버정보/20260716_리소스배포_랜딩.xlsx
+++ b/서버정보/20260716_리소스배포_랜딩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7450998-4E38-45E5-99C8-27FEFF3ACDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7CC838-B50D-46EE-BA93-17BC58F6483D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2935,10 +2935,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D32s_v5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2952,6 +2948,10 @@
   </si>
   <si>
     <t>l-if-cpspsol01-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3436,7 +3436,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3753,12 +3753,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6230,11 +6224,11 @@
       <c r="B11" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="106" t="str" cm="1">
+      <c r="C11" s="88" t="str" cm="1">
         <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
         <v>IF</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="88" t="s">
         <v>145</v>
       </c>
       <c r="E11" s="88" t="s">
@@ -6247,7 +6241,7 @@
         <v>334</v>
       </c>
       <c r="H11" s="88" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I11" s="88">
         <v>32</v>
@@ -6265,9 +6259,9 @@
         <v>292</v>
       </c>
       <c r="N11" s="97" t="s">
-        <v>335</v>
-      </c>
-      <c r="O11" s="107" t="str">
+        <v>339</v>
+      </c>
+      <c r="O11" s="98" t="str">
         <f>SUBSTITUTE(F11,"hazr-","")&amp;"-osdisk"</f>
         <v>l-if-cpspsol01-osdisk</v>
       </c>
@@ -6277,9 +6271,9 @@
       <c r="Q11" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="R11" s="106"/>
+      <c r="R11" s="88"/>
       <c r="S11" s="88"/>
-      <c r="T11" s="106"/>
+      <c r="T11" s="88"/>
       <c r="U11" s="88" t="str">
         <f>SUBSTITUTE(F11,"hazr-","")&amp;"-nic"</f>
         <v>l-if-cpspsol01-nic</v>
@@ -6890,7 +6884,7 @@
         <v>IF</v>
       </c>
       <c r="D11" s="69" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E11" s="69" t="s">
         <v>24</v>
@@ -6899,7 +6893,7 @@
         <v>333</v>
       </c>
       <c r="G11" s="75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H11" s="69" t="s">
         <v>121</v>
@@ -6908,7 +6902,7 @@
         <v>2048</v>
       </c>
       <c r="J11" s="75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K11" s="75" t="s">
         <v>121</v>
@@ -16803,9 +16797,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16953,26 +16950,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16996,9 +16982,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>